--- a/public/downloads/leaveform.xlsx
+++ b/public/downloads/leaveform.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\DE INFO\BHC\VAMED PROJ\Worked on\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\getinnotized\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADF2D98F-BA27-48DE-9CED-5EEC5EBC0BC5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="8925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16755" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="leave" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>APPLICATION FOR LEAVE</t>
   </si>
@@ -101,12 +100,6 @@
   </si>
   <si>
     <t>Accra</t>
-  </si>
-  <si>
-    <t>Joshua ELO</t>
-  </si>
-  <si>
-    <t>Security</t>
   </si>
   <si>
     <t>-</t>
@@ -124,22 +117,12 @@
       </rPr>
       <t xml:space="preserve">             </t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Annual Leave for 2018 completed </t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
@@ -498,6 +481,99 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -510,12 +586,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -561,21 +631,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -593,78 +648,6 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,7 +686,7 @@
         <xdr:cNvPr id="1025" name="Picture 1" descr="vamed_Logo_RGB_TO BE USED">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000001040000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -816,23 +799,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -868,23 +834,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1060,7 +1009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1086,16 +1035,16 @@
       <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="29"/>
       <c r="J2" s="5"/>
     </row>
@@ -1112,16 +1061,16 @@
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
       <c r="I4" s="29"/>
       <c r="J4" s="5"/>
     </row>
@@ -1160,19 +1109,15 @@
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
-      <c r="B8" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="96" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="97"/>
-      <c r="G8" s="98"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50"/>
       <c r="H8" s="42"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="51"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
@@ -1208,25 +1153,17 @@
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
-      <c r="B12" s="52">
-        <v>7</v>
-      </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="101">
-        <v>43436</v>
-      </c>
-      <c r="E12" s="102"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="56"/>
       <c r="F12" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="103">
-        <v>43442</v>
-      </c>
-      <c r="H12" s="103"/>
-      <c r="I12" s="48">
-        <v>43413</v>
-      </c>
-      <c r="J12" s="49"/>
+        <v>27</v>
+      </c>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="80"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="18"/>
@@ -1242,51 +1179,51 @@
     </row>
     <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="92">
-        <v>7</v>
-      </c>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="72">
+        <v>0</v>
+      </c>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="33"/>
     </row>
     <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="92">
+      <c r="B16" s="65"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="72">
         <f>B12</f>
-        <v>7</v>
-      </c>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90">
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70">
         <f>D15-D16</f>
         <v>0</v>
       </c>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
       <c r="H17" s="46"/>
       <c r="I17" s="44"/>
       <c r="J17" s="45"/>
@@ -1304,11 +1241,11 @@
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
@@ -1320,45 +1257,45 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="68"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="97"/>
       <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="65" t="s">
+      <c r="A21" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="68"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="97"/>
       <c r="J22" s="35"/>
     </row>
     <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1390,16 +1327,16 @@
     <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="37"/>
       <c r="B25" s="38"/>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="95"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="75"/>
     </row>
     <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
@@ -1415,46 +1352,46 @@
     </row>
     <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="69" t="s">
+      <c r="A28" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69" t="s">
+      <c r="B28" s="58"/>
+      <c r="C28" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="80" t="s">
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="81"/>
-      <c r="J28" s="82"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="78"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="70"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="76"/>
+      <c r="A29" s="59"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="100"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="71"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="79"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="103"/>
     </row>
     <row r="31" spans="1:10" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
@@ -1473,46 +1410,46 @@
         <v>21</v>
       </c>
       <c r="B32" s="21"/>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="80" t="s">
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="I32" s="81"/>
-      <c r="J32" s="82"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="78"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="26" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="22"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="76"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="100"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B34" s="24"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="79"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="103"/>
     </row>
     <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1520,103 +1457,86 @@
         <v>22</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69" t="s">
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B37" s="22"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="27"/>
       <c r="B38" s="24"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
     </row>
     <row r="39" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="56"/>
+      <c r="A40" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="85"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="57"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="59"/>
+      <c r="A41" s="86"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="88"/>
     </row>
     <row r="42" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="60"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="62"/>
+      <c r="A42" s="89"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="90"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C32:G34"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A28:B30"/>
-    <mergeCell ref="C28:G30"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="H28:J28"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="B12:C12"/>
@@ -1633,6 +1553,23 @@
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="H33:J34"/>
     <mergeCell ref="C36:G38"/>
+    <mergeCell ref="C32:G34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A28:B30"/>
+    <mergeCell ref="C28:G30"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="1.1417322830000001" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
